--- a/cp-date/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/cp-date/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:13:06+00:00</t>
+    <t>2026-05-05T12:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-date/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/cp-date/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:29:58+00:00</t>
+    <t>2026-05-06T12:23:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
